--- a/artfynd/S 2453-2024 artfynd.xlsx
+++ b/artfynd/S 2453-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY189"/>
+  <dimension ref="A1:AZ189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359455</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394156</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394198</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394385</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394403</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394470</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394485</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447405</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447420</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,6 +1733,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394476</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1785,6 +1840,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394493</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394425</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447425</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,6 +2158,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394175</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2189,6 +2264,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394481</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2291,6 +2371,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394942</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2392,6 +2477,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394504</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2493,6 +2583,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394384</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2594,6 +2689,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394421</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2695,6 +2795,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394463</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2796,6 +2901,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394490</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2897,6 +3007,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447426</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3003,6 +3118,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394176</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3104,6 +3224,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394381</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3215,6 +3340,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394388</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3316,6 +3446,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394406</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3417,6 +3552,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394462</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3518,6 +3658,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394409</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3619,6 +3764,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394475</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3720,6 +3870,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394489</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3831,6 +3986,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436386</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3932,6 +4092,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394377</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4033,6 +4198,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394389</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4171,6 +4341,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436390</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4272,6 +4447,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394153</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4373,6 +4553,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394442</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4474,6 +4659,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394488</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4575,6 +4765,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394471</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4676,6 +4871,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394473</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4777,6 +4977,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394497</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4878,6 +5083,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394418</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4979,6 +5189,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394447</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5080,6 +5295,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394449</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5181,6 +5401,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447410</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5282,6 +5507,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394399</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5383,6 +5613,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447404</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5484,6 +5719,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394371</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5585,6 +5825,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394155</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5686,6 +5931,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394426</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5787,6 +6037,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394427</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5888,6 +6143,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394428</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5989,6 +6249,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394408</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6090,6 +6355,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394479</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6191,6 +6461,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394413</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6292,6 +6567,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394478</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6393,6 +6673,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394461</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6494,6 +6779,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394438</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6595,6 +6885,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394383</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6696,6 +6991,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394482</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6797,6 +7097,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394420</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6903,6 +7208,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394158</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7004,6 +7314,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359452</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7105,6 +7420,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394393</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7206,6 +7526,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394402</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7307,6 +7632,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394411</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7408,6 +7738,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394431</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7509,6 +7844,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447413</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7610,6 +7950,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447422</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7721,6 +8066,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436387</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7827,6 +8177,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394400</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7933,6 +8288,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394472</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8034,6 +8394,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359451</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8135,6 +8500,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394387</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8236,6 +8606,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394419</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8337,6 +8712,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394441</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8438,6 +8818,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394491</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8539,6 +8924,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447395</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8640,6 +9030,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447399</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8741,6 +9136,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394487</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8842,6 +9242,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394154</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8943,6 +9348,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394199</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9044,6 +9454,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394443</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9146,6 +9561,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394450</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9248,6 +9668,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394492</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9349,6 +9774,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394202</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9450,6 +9880,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394434</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9551,6 +9986,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394435</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9652,6 +10092,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394445</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9753,6 +10198,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394459</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9854,6 +10304,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394502</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9955,6 +10410,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394458</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10061,6 +10521,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394495</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10162,6 +10627,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394366</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10263,6 +10733,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394174</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10364,6 +10839,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394203</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10465,6 +10945,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394382</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10566,6 +11051,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394415</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10667,6 +11157,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394436</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10768,6 +11263,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394437</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10869,6 +11369,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394448</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10970,6 +11475,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394501</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11098,6 +11608,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114186087</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11226,6 +11741,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205089</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11327,6 +11847,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394396</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11442,6 +11967,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447429</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11543,6 +12073,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394378</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11644,6 +12179,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394380</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11745,6 +12285,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394395</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11846,6 +12391,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394430</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11947,6 +12497,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447402</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12048,6 +12603,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447424</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12172,6 +12732,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82296345</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12296,6 +12861,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114186026</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12420,6 +12990,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122670727</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12544,6 +13119,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131205070</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12653,6 +13233,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96483470</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12772,6 +13357,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713857</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12891,6 +13481,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121970840</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12992,6 +13587,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394379</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13093,6 +13693,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394391</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13194,6 +13799,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394394</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13295,6 +13905,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394397</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13396,6 +14011,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394432</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13497,6 +14117,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447423</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13598,6 +14223,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359453</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13699,6 +14329,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394200</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13800,6 +14435,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394433</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13901,6 +14541,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394446</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14002,6 +14647,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394499</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14126,6 +14776,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121970844</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14250,6 +14905,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121970843</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14375,6 +15035,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713474</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14481,6 +15146,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394422</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14587,6 +15257,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394423</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14693,6 +15368,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394424</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14817,6 +15497,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713763</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14918,6 +15603,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447396</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15019,6 +15709,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447411</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15121,6 +15816,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436385</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15228,6 +15928,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394201</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15330,6 +16035,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394457</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15437,6 +16147,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394477</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15544,6 +16259,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394412</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15651,6 +16371,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394416</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15758,6 +16483,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394474</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15859,6 +16589,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394149</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15978,6 +16713,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112140797</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16097,6 +16837,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112140792</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16198,6 +16943,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359486</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16299,6 +17049,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359488</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16400,6 +17155,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394545</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16501,6 +17261,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359478</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16602,6 +17367,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394546</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16703,6 +17473,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394609</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16804,6 +17579,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394547</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16905,6 +17685,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394608</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17006,6 +17791,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359473</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17107,6 +17897,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394330</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17208,6 +18003,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359476</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17309,6 +18109,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359477</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17410,6 +18215,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359479</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17511,6 +18321,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359484</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17612,6 +18427,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359487</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17713,6 +18533,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359489</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17814,6 +18639,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359490</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17931,6 +18761,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436383</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18032,6 +18867,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359472</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18134,6 +18974,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359474</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18258,6 +19103,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1754011</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18382,6 +19232,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1754012</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18495,6 +19350,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99472691</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18614,6 +19474,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123060051</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18716,6 +19581,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/394386</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18827,6 +19697,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3054110</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18938,6 +19813,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4149791</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19045,6 +19925,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4173197</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19143,6 +20028,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4173198</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19250,6 +20140,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4174254</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19355,6 +20250,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68051891</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19475,6 +20375,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123060275</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19594,6 +20499,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82296400</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19703,6 +20613,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104245641</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19829,6 +20744,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55933470</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19937,6 +20857,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70368006</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20045,6 +20970,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70368126</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20158,6 +21088,11 @@
       <c r="AY187" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86311432</t>
         </is>
       </c>
     </row>
@@ -20271,6 +21206,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99439082</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20371,8 +21311,203 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70330061</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>